--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128260561</v>
+        <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>91680</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3215</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>667956</v>
+        <v>667842</v>
       </c>
       <c r="R2" t="n">
-        <v>6691635</v>
+        <v>6691599</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -761,6 +761,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -776,16 +791,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128260561</t>
+          <t>https://artportalen.se/Sighting/136974092</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126056868</v>
+        <v>128260561</v>
       </c>
       <c r="B3" t="n">
-        <v>57141</v>
+        <v>91680</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,42 +808,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>3215</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>668245</v>
+        <v>667956</v>
       </c>
       <c r="R3" t="n">
-        <v>6691768</v>
+        <v>6691635</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,12 +862,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2025-09-06</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,60 +887,60 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ingemar Södergren, Shanti Wittmar</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126056868</t>
+          <t>https://artportalen.se/Sighting/128260561</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125855912</v>
+        <v>136974105</v>
       </c>
       <c r="B4" t="n">
-        <v>4781</v>
+        <v>75566</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>6426</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Östensbo-Bennebo, Upl</t>
+          <t>Ladängsskogen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>668276</v>
+        <v>667774</v>
       </c>
       <c r="R4" t="n">
-        <v>6691767</v>
+        <v>6691616</v>
       </c>
       <c r="S4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,12 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -970,31 +980,46 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Signe Propst</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125855912</t>
+          <t>https://artportalen.se/Sighting/136974105</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125984242</v>
+        <v>126056868</v>
       </c>
       <c r="B5" t="n">
-        <v>99035</v>
+        <v>57141</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1002,37 +1027,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Östensbo-Bennebo, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>667892</v>
+        <v>668245</v>
       </c>
       <c r="R5" t="n">
-        <v>6691648</v>
+        <v>6691768</v>
       </c>
       <c r="S5" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1076,16 +1106,327 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johanna Sollén Mattsson</t>
+          <t>Ingemar Södergren, Shanti Wittmar</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126056868</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>125855912</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4781</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>102306</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granbarkgnagare</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Microbregma emarginatum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>668276</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6691767</v>
+      </c>
+      <c r="S6" t="n">
+        <v>12</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Signe Propst</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125855912</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136974093</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ladängsskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>667852</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6691618</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Ingemar Södergren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136974093</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>125984242</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Östensbo-Bennebo, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>667892</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6691648</v>
+      </c>
+      <c r="S8" t="n">
+        <v>12</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Valö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-08</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Johanna Sollén Mattsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Johanna Sollén Mattsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/125984242</t>
         </is>
@@ -1097,6 +1438,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136974105</v>
       </c>
       <c r="B4" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136974093</v>
       </c>
       <c r="B7" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136974105</v>
       </c>
       <c r="B4" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136974093</v>
       </c>
       <c r="B7" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1254,11 +1254,7 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Ladängsskogen, Upl</t>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136974105</v>
       </c>
       <c r="B4" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136974093</v>
       </c>
       <c r="B7" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136974105</v>
       </c>
       <c r="B4" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136974093</v>
       </c>
       <c r="B7" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136974105</v>
       </c>
       <c r="B4" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136974093</v>
       </c>
       <c r="B7" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136974105</v>
       </c>
       <c r="B4" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92185</v>
+        <v>92186</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136974105</v>
       </c>
       <c r="B4" t="n">
-        <v>75610</v>
+        <v>75611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 33800-2024 artfynd.xlsx
+++ b/artfynd/A 33800-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136974092</v>
       </c>
       <c r="B2" t="n">
-        <v>92186</v>
+        <v>92189</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136974105</v>
       </c>
       <c r="B4" t="n">
-        <v>75611</v>
+        <v>75614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1228,7 +1228,7 @@
         <v>136974093</v>
       </c>
       <c r="B7" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
